--- a/tables/if_per_resource_metrics.xlsx
+++ b/tables/if_per_resource_metrics.xlsx
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.117</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.059</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.029</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>0.046</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.033</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.280</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.117</t>
         </is>
       </c>
     </row>
@@ -742,17 +742,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.120</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>0.034</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.053</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.019</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.445</t>
         </is>
       </c>
     </row>

--- a/tables/if_per_resource_metrics.xlsx
+++ b/tables/if_per_resource_metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.190</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.102</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.118</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.183</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.151</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.127</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.402</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.109</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.064</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.110</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.062</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.370</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.129</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.145</t>
         </is>
       </c>
     </row>
@@ -742,17 +742,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.123</t>
         </is>
       </c>
     </row>
@@ -770,17 +770,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.143</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.163</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.059</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.102</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.526</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>

--- a/tables/if_per_resource_metrics.xlsx
+++ b/tables/if_per_resource_metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.060</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.119</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.504</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.135</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.146</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.100</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.172</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.486</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.134</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>0.437</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.118</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>0.056</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.110</t>
+          <t>0.095</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.370</t>
+          <t>0.435</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.125</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.059</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.101</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.038</t>
         </is>
       </c>
     </row>
@@ -742,17 +742,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.081</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.136</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.144</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.227</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>0.104</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>0.077</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.133</t>
         </is>
       </c>
     </row>

--- a/tables/if_per_resource_metrics.xlsx
+++ b/tables/if_per_resource_metrics.xlsx
@@ -462,17 +462,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.102</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.068</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.118</t>
         </is>
       </c>
     </row>
@@ -518,17 +518,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.183</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.100</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.538</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.151</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.127</t>
         </is>
       </c>
     </row>
@@ -602,17 +602,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>0.402</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.109</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.064</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.110</t>
         </is>
       </c>
     </row>
@@ -658,17 +658,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.062</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>0.370</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.129</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.533</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.145</t>
         </is>
       </c>
     </row>
@@ -742,17 +742,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.123</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.082</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.143</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.163</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.059</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.102</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.526</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.139</t>
         </is>
       </c>
     </row>

--- a/tables/if_per_resource_metrics.xlsx
+++ b/tables/if_per_resource_metrics.xlsx
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Resource</t>
+          <t>Ressource</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Train Rows</t>
+          <t>Trainingszeilen</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Val Rows</t>
+          <t>Testzeilen</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
